--- a/public/examples/france-south-loop.xlsx
+++ b/public/examples/france-south-loop.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Trip" sheetId="1" r:id="rId1"/>
-    <sheet name="Schedule" sheetId="2" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" r:id="rId3"/>
+    <sheet name="Steps" sheetId="2" r:id="rId2"/>
+    <sheet name="Hotels" sheetId="3" r:id="rId3"/>
+    <sheet name="Cash" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -462,234 +463,218 @@
         <v>notes</v>
       </c>
       <c r="B8" t="str">
-        <v>Built-in sample: TLV→Paris (2 nights) → TGV Marseille → 4-day Provence car loop → MRS→Napoli. Duplicate to make it yours.</v>
+        <v>Sample: TLV→Paris (2n) → TGV Marseille → Provence car loop east→west (Cassis→Aix→Avignon→Arles) → MRS→Napoli. Duplicate to make it yours.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>How to use</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Edit the Steps sheet for day plans (sights, food, drives, flights). Use Hotels for stays. Cash is a read-only spend snapshot.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Row 2 under each table shows Required/Optional and the preferred format. Import also accepts other common date/time styles.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Preferred date: YYYY-MM-DD · Preferred time: HH:MM (24h).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:T35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
-        <v>date</v>
+        <v>Start</v>
       </c>
       <c r="C1" t="str">
-        <v>end_date</v>
+        <v>End</v>
       </c>
       <c r="D1" t="str">
-        <v>start</v>
+        <v>Type</v>
       </c>
       <c r="E1" t="str">
-        <v>end</v>
+        <v>Title</v>
       </c>
       <c r="F1" t="str">
-        <v>type</v>
+        <v>Place</v>
       </c>
       <c r="G1" t="str">
-        <v>title</v>
+        <v>City</v>
       </c>
       <c r="H1" t="str">
-        <v>place</v>
+        <v>From</v>
       </c>
       <c r="I1" t="str">
-        <v>city</v>
+        <v>To</v>
       </c>
       <c r="J1" t="str">
-        <v>from</v>
+        <v>Confirm</v>
       </c>
       <c r="K1" t="str">
-        <v>to</v>
+        <v>Cost</v>
       </c>
       <c r="L1" t="str">
-        <v>confirm</v>
+        <v>Currency</v>
       </c>
       <c r="M1" t="str">
-        <v>cost</v>
+        <v>Status</v>
       </c>
       <c r="N1" t="str">
-        <v>currency</v>
+        <v>Notes</v>
       </c>
       <c r="O1" t="str">
-        <v>status</v>
+        <v>URL</v>
       </c>
       <c r="P1" t="str">
-        <v>notes</v>
+        <v>Tags</v>
       </c>
       <c r="Q1" t="str">
-        <v>url</v>
+        <v>Lat</v>
       </c>
       <c r="R1" t="str">
-        <v>tags</v>
+        <v>Lon</v>
       </c>
       <c r="S1" t="str">
-        <v>lat</v>
+        <v>Lat to</v>
       </c>
       <c r="T1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="U1" t="str">
-        <v>lat_to</v>
-      </c>
-      <c r="V1" t="str">
-        <v>lon_to</v>
-      </c>
-      <c r="W1" t="str">
-        <v>wikidata</v>
-      </c>
-      <c r="X1" t="str">
-        <v>osm_id</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>geocode_query</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>updated_at</v>
+        <v>Lon to</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>F01</v>
+        <v>Required · YYYY-MM-DD</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-18</v>
+        <v>Optional · HH:MM (24h)</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Optional · HH:MM (24h)</v>
       </c>
       <c r="D2" t="str">
-        <v>11:25</v>
+        <v>Required · flight, train, bus, ferry, drive, sight, restaurant, activity, city, note, other</v>
       </c>
       <c r="E2" t="str">
-        <v>14:55</v>
+        <v>Required · free text</v>
       </c>
       <c r="F2" t="str">
-        <v>flight</v>
+        <v>Optional · free text</v>
       </c>
       <c r="G2" t="str">
-        <v>AF565</v>
+        <v>Optional · free text</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Optional · place or IATA</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Optional · place or IATA</v>
       </c>
       <c r="J2" t="str">
-        <v>TLV</v>
+        <v>Optional · booking ref</v>
       </c>
       <c r="K2" t="str">
-        <v>CDG</v>
+        <v>Optional · number ≥ 0</v>
       </c>
       <c r="L2" t="str">
-        <v>AF565-88XK</v>
-      </c>
-      <c r="M2">
-        <v>420</v>
+        <v>Optional · 3-letter code (EUR)</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Optional · planned / booked / done / cancelled</v>
       </c>
       <c r="N2" t="str">
-        <v>EUR</v>
+        <v>Optional · free text</v>
       </c>
       <c r="O2" t="str">
-        <v>booked</v>
+        <v>Optional · https://…</v>
       </c>
       <c r="P2" t="str">
-        <v>Window seat; Terminal 2E</v>
+        <v>Optional · comma-separated</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>Optional · decimal degrees</v>
       </c>
       <c r="R2" t="str">
-        <v>outbound</v>
-      </c>
-      <c r="S2">
-        <v>32.0114</v>
-      </c>
-      <c r="T2">
-        <v>34.8867</v>
-      </c>
-      <c r="U2">
-        <v>49.0097</v>
-      </c>
-      <c r="V2">
-        <v>2.5479</v>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Optional · decimal degrees</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>D01</v>
+        <v>2026-09-18</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-18</v>
+        <v>11:25</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>14:55</v>
       </c>
       <c r="D3" t="str">
-        <v>15:40</v>
+        <v>flight</v>
       </c>
       <c r="E3" t="str">
-        <v>16:25</v>
+        <v>AF565</v>
       </c>
       <c r="F3" t="str">
-        <v>train</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>RER B to Paris</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>TLV</v>
       </c>
       <c r="I3" t="str">
-        <v>Paris</v>
+        <v>CDG</v>
       </c>
       <c r="J3" t="str">
-        <v>CDG</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Gare du Nord</v>
+        <v>AF565-88XK</v>
+      </c>
+      <c r="K3">
+        <v>420</v>
       </c>
       <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3">
-        <v>11.8</v>
+        <v>EUR</v>
+      </c>
+      <c r="M3" t="str">
+        <v>booked</v>
       </c>
       <c r="N3" t="str">
-        <v>EUR</v>
+        <v>Window seat; Terminal 2E</v>
       </c>
       <c r="O3" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P3" t="str">
-        <v>Airport ticket</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
+        <v>outbound</v>
+      </c>
+      <c r="Q3">
+        <v>32.0114</v>
+      </c>
+      <c r="R3">
+        <v>34.8867</v>
       </c>
       <c r="S3">
         <v>49.0097</v>
@@ -697,490 +682,370 @@
       <c r="T3">
         <v>2.5479</v>
       </c>
-      <c r="U3">
-        <v>48.8809</v>
-      </c>
-      <c r="V3">
-        <v>2.3553</v>
-      </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>H01</v>
+        <v>2026-09-18</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-09-18</v>
+        <v>15:40</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-09-20</v>
+        <v>16:25</v>
       </c>
       <c r="D4" t="str">
-        <v>16:00</v>
+        <v>train</v>
       </c>
       <c r="E4" t="str">
-        <v>11:00</v>
+        <v>RER B to Paris</v>
       </c>
       <c r="F4" t="str">
-        <v>hotel</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Hôtel Jeanne d'Arc</v>
+        <v>Paris</v>
       </c>
       <c r="H4" t="str">
-        <v>Hôtel Jeanne d'Arc Le Marais</v>
+        <v>CDG</v>
       </c>
       <c r="I4" t="str">
-        <v>Paris</v>
+        <v>Gare du Nord</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="K4">
+        <v>11.8</v>
       </c>
       <c r="L4" t="str">
-        <v>HJD-1942</v>
-      </c>
-      <c r="M4">
-        <v>280</v>
+        <v>EUR</v>
+      </c>
+      <c r="M4" t="str">
+        <v>booked</v>
       </c>
       <c r="N4" t="str">
-        <v>EUR</v>
+        <v>Airport ticket</v>
       </c>
       <c r="O4" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P4" t="str">
-        <v>2 nights; Marais</v>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>base</v>
+        <v/>
+      </c>
+      <c r="Q4">
+        <v>49.0097</v>
+      </c>
+      <c r="R4">
+        <v>2.5479</v>
       </c>
       <c r="S4">
-        <v>48.8555</v>
+        <v>48.8809</v>
       </c>
       <c r="T4">
-        <v>2.3615</v>
-      </c>
-      <c r="W4" t="str">
-        <v/>
-      </c>
-      <c r="X4" t="str">
-        <v/>
-      </c>
-      <c r="Y4" t="str">
-        <v/>
-      </c>
-      <c r="Z4" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v>2.3553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>R01</v>
+        <v>2026-09-18</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-18</v>
+        <v>20:00</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D5" t="str">
-        <v>20:00</v>
+        <v>restaurant</v>
       </c>
       <c r="E5" t="str">
-        <v>22:00</v>
+        <v>Dinner Breizh Café</v>
       </c>
       <c r="F5" t="str">
-        <v>restaurant</v>
+        <v>Breizh Café du Marais</v>
       </c>
       <c r="G5" t="str">
-        <v>Dinner Breizh Café</v>
+        <v>Paris</v>
       </c>
       <c r="H5" t="str">
-        <v>Breizh Café</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="K5">
+        <v>45</v>
       </c>
       <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5">
-        <v>55</v>
+        <v>EUR</v>
+      </c>
+      <c r="M5" t="str">
+        <v>booked</v>
       </c>
       <c r="N5" t="str">
-        <v>EUR</v>
+        <v>Galettes near the hotel</v>
       </c>
       <c r="O5" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P5" t="str">
-        <v>Crêpes; reservation</v>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5">
+        <v>crepes</v>
+      </c>
+      <c r="Q5">
         <v>48.8566</v>
       </c>
-      <c r="T5">
+      <c r="R5">
         <v>2.3622</v>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
-        <v/>
-      </c>
-      <c r="Y5" t="str">
-        <v/>
-      </c>
-      <c r="Z5" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>S01</v>
+        <v>2026-09-19</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-19</v>
+        <v>09:30</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>13:00</v>
       </c>
       <c r="D6" t="str">
-        <v>09:30</v>
+        <v>sight</v>
       </c>
       <c r="E6" t="str">
-        <v>12:00</v>
+        <v>Louvre</v>
       </c>
       <c r="F6" t="str">
-        <v>sight</v>
+        <v>Musée du Louvre</v>
       </c>
       <c r="G6" t="str">
-        <v>Louvre</v>
+        <v>Paris</v>
       </c>
       <c r="H6" t="str">
-        <v>Musée du Louvre</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
-      <c r="K6" t="str">
-        <v/>
+      <c r="K6">
+        <v>22</v>
       </c>
       <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6">
-        <v>22</v>
+        <v>EUR</v>
+      </c>
+      <c r="M6" t="str">
+        <v>booked</v>
       </c>
       <c r="N6" t="str">
-        <v>EUR</v>
+        <v>Timed entry</v>
       </c>
       <c r="O6" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P6" t="str">
-        <v>Timed entry 09:30</v>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
         <v>museum</v>
       </c>
-      <c r="S6">
+      <c r="Q6">
         <v>48.8606</v>
       </c>
-      <c r="T6">
+      <c r="R6">
         <v>2.3376</v>
-      </c>
-      <c r="W6" t="str">
-        <v>Q19675</v>
-      </c>
-      <c r="X6" t="str">
-        <v/>
-      </c>
-      <c r="Y6" t="str">
-        <v/>
-      </c>
-      <c r="Z6" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>S02</v>
+        <v>2026-09-19</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-09-19</v>
+        <v>13:30</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>15:00</v>
       </c>
       <c r="D7" t="str">
-        <v>14:00</v>
+        <v>restaurant</v>
       </c>
       <c r="E7" t="str">
-        <v>16:00</v>
+        <v>Lunch Café Marly</v>
       </c>
       <c r="F7" t="str">
-        <v>sight</v>
+        <v>Café Marly</v>
       </c>
       <c r="G7" t="str">
-        <v>Sainte-Chapelle</v>
+        <v>Paris</v>
       </c>
       <c r="H7" t="str">
-        <v>Sainte-Chapelle</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
-      <c r="K7" t="str">
-        <v/>
+      <c r="K7">
+        <v>55</v>
       </c>
       <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7">
-        <v>19</v>
+        <v>EUR</v>
+      </c>
+      <c r="M7" t="str">
+        <v>planned</v>
       </c>
       <c r="N7" t="str">
-        <v>EUR</v>
+        <v>Louvre courtyard</v>
       </c>
       <c r="O7" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P7" t="str">
-        <v>Combined ticket w/ Conciergerie</v>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v>gothic</v>
-      </c>
-      <c r="S7">
-        <v>48.8554</v>
-      </c>
-      <c r="T7">
-        <v>2.345</v>
-      </c>
-      <c r="W7" t="str">
-        <v>Q190348</v>
-      </c>
-      <c r="X7" t="str">
-        <v/>
-      </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
-      <c r="Z7" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v/>
+      </c>
+      <c r="Q7">
+        <v>48.8611</v>
+      </c>
+      <c r="R7">
+        <v>2.3356</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>R02</v>
+        <v>2026-09-19</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-09-19</v>
+        <v>16:00</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>17:30</v>
       </c>
       <c r="D8" t="str">
-        <v>19:30</v>
+        <v>sight</v>
       </c>
       <c r="E8" t="str">
-        <v>21:30</v>
+        <v>Sainte-Chapelle</v>
       </c>
       <c r="F8" t="str">
-        <v>restaurant</v>
+        <v>Sainte-Chapelle</v>
       </c>
       <c r="G8" t="str">
-        <v>Dinner Chez Janou</v>
+        <v>Paris</v>
       </c>
       <c r="H8" t="str">
-        <v>Chez Janou</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
-      <c r="K8" t="str">
-        <v/>
+      <c r="K8">
+        <v>13</v>
       </c>
       <c r="L8" t="str">
-        <v>CJ-09</v>
-      </c>
-      <c r="M8">
-        <v>70</v>
+        <v>EUR</v>
+      </c>
+      <c r="M8" t="str">
+        <v>booked</v>
       </c>
       <c r="N8" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O8" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P8" t="str">
-        <v>Provençal; outdoor if warm</v>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8">
-        <v>48.8578</v>
-      </c>
-      <c r="T8">
-        <v>2.3665</v>
-      </c>
-      <c r="W8" t="str">
-        <v/>
-      </c>
-      <c r="X8" t="str">
-        <v/>
-      </c>
-      <c r="Y8" t="str">
-        <v/>
-      </c>
-      <c r="Z8" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v>gothic</v>
+      </c>
+      <c r="Q8">
+        <v>48.8554</v>
+      </c>
+      <c r="R8">
+        <v>2.345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>S03</v>
+        <v>2026-09-19</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-09-20</v>
+        <v>20:00</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D9" t="str">
-        <v>10:00</v>
+        <v>restaurant</v>
       </c>
       <c r="E9" t="str">
-        <v>12:30</v>
+        <v>Dinner Chez Janou</v>
       </c>
       <c r="F9" t="str">
-        <v>sight</v>
+        <v>Chez Janou</v>
       </c>
       <c r="G9" t="str">
-        <v>Musée d'Orsay</v>
+        <v>Paris</v>
       </c>
       <c r="H9" t="str">
-        <v>Musée d'Orsay</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
-      <c r="K9" t="str">
-        <v/>
+      <c r="K9">
+        <v>50</v>
       </c>
       <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9">
-        <v>16</v>
+        <v>EUR</v>
+      </c>
+      <c r="M9" t="str">
+        <v>planned</v>
       </c>
       <c r="N9" t="str">
-        <v>EUR</v>
+        <v>Provençal; Place des Vosges</v>
       </c>
       <c r="O9" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P9" t="str">
-        <v>Impressionists</v>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v>museum</v>
-      </c>
-      <c r="S9">
-        <v>48.86</v>
-      </c>
-      <c r="T9">
-        <v>2.3266</v>
-      </c>
-      <c r="W9" t="str">
-        <v>Q23402</v>
-      </c>
-      <c r="X9" t="str">
-        <v/>
-      </c>
-      <c r="Y9" t="str">
-        <v/>
-      </c>
-      <c r="Z9" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v/>
+      </c>
+      <c r="Q9">
+        <v>48.8578</v>
+      </c>
+      <c r="R9">
+        <v>2.3665</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>T01</v>
+        <v>2026-09-20</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-20</v>
+        <v>09:00</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>11:30</v>
       </c>
       <c r="D10" t="str">
-        <v>14:18</v>
+        <v>sight</v>
       </c>
       <c r="E10" t="str">
-        <v>17:28</v>
+        <v>Musée d'Orsay</v>
       </c>
       <c r="F10" t="str">
-        <v>train</v>
+        <v>Musée d'Orsay</v>
       </c>
       <c r="G10" t="str">
-        <v>TGV 6175</v>
+        <v>Paris</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -1189,481 +1054,376 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Paris Gare de Lyon</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Marseille St-Charles</v>
+        <v/>
+      </c>
+      <c r="K10">
+        <v>16</v>
       </c>
       <c r="L10" t="str">
-        <v>TGV-6175-AS</v>
-      </c>
-      <c r="M10">
-        <v>89</v>
+        <v>EUR</v>
+      </c>
+      <c r="M10" t="str">
+        <v>booked</v>
       </c>
       <c r="N10" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O10" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P10" t="str">
-        <v>2nd class; seat 12A</v>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v>tgv</v>
-      </c>
-      <c r="S10">
-        <v>48.8443</v>
-      </c>
-      <c r="T10">
-        <v>2.3735</v>
-      </c>
-      <c r="U10">
-        <v>43.3027</v>
-      </c>
-      <c r="V10">
-        <v>5.3806</v>
-      </c>
-      <c r="W10" t="str">
-        <v/>
-      </c>
-      <c r="X10" t="str">
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <v/>
-      </c>
-      <c r="Z10" t="str">
-        <v>2026-09-10T17:55:43.472Z</v>
+        <v>museum</v>
+      </c>
+      <c r="Q10">
+        <v>48.86</v>
+      </c>
+      <c r="R10">
+        <v>2.3266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>H02</v>
+        <v>2026-09-20</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-09-20</v>
+        <v>12:46</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-09-21</v>
+        <v>16:14</v>
       </c>
       <c r="D11" t="str">
-        <v>18:30</v>
+        <v>train</v>
       </c>
       <c r="E11" t="str">
-        <v>10:00</v>
+        <v>TGV 6175</v>
       </c>
       <c r="F11" t="str">
-        <v>hotel</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>Hôtel La Résidence du Vieux-Port</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>La Résidence du Vieux-Port</v>
+        <v>Paris Gare de Lyon</v>
       </c>
       <c r="I11" t="str">
-        <v>Marseille</v>
+        <v>Marseille St-Charles</v>
       </c>
       <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
+        <v>TGV6175</v>
+      </c>
+      <c r="K11">
+        <v>89</v>
       </c>
       <c r="L11" t="str">
-        <v>LRP-772</v>
-      </c>
-      <c r="M11">
-        <v>145</v>
+        <v>EUR</v>
+      </c>
+      <c r="M11" t="str">
+        <v>booked</v>
       </c>
       <c r="N11" t="str">
-        <v>EUR</v>
+        <v>1st class</v>
       </c>
       <c r="O11" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P11" t="str">
-        <v>1 night before car pickup</v>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="Q11">
+        <v>48.8443</v>
+      </c>
+      <c r="R11">
+        <v>2.3735</v>
       </c>
       <c r="S11">
-        <v>43.2951</v>
+        <v>43.3027</v>
       </c>
       <c r="T11">
-        <v>5.3738</v>
-      </c>
-      <c r="W11" t="str">
-        <v/>
-      </c>
-      <c r="X11" t="str">
-        <v/>
-      </c>
-      <c r="Y11" t="str">
-        <v/>
-      </c>
-      <c r="Z11" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>5.3805</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>R03</v>
+        <v>2026-09-20</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-20</v>
+        <v>20:00</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>22:30</v>
       </c>
       <c r="D12" t="str">
-        <v>20:30</v>
+        <v>restaurant</v>
       </c>
       <c r="E12" t="str">
-        <v>22:30</v>
+        <v>Bouillabaisse Chez Fonfon</v>
       </c>
       <c r="F12" t="str">
-        <v>restaurant</v>
+        <v>Chez Fonfon</v>
       </c>
       <c r="G12" t="str">
-        <v>Bouillabaisse Chez Fonfon</v>
+        <v>Marseille</v>
       </c>
       <c r="H12" t="str">
-        <v>Chez Fonfon</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>Marseille</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
-      <c r="K12" t="str">
-        <v/>
+      <c r="K12">
+        <v>70</v>
       </c>
       <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12">
-        <v>85</v>
+        <v>EUR</v>
+      </c>
+      <c r="M12" t="str">
+        <v>booked</v>
       </c>
       <c r="N12" t="str">
-        <v>EUR</v>
+        <v>Vallon des Auffes</v>
       </c>
       <c r="O12" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P12" t="str">
-        <v>Vieux-Port classic</v>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
         <v>seafood</v>
       </c>
-      <c r="S12">
+      <c r="Q12">
         <v>43.2905</v>
       </c>
-      <c r="T12">
+      <c r="R12">
         <v>5.3619</v>
-      </c>
-      <c r="W12" t="str">
-        <v/>
-      </c>
-      <c r="X12" t="str">
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <v/>
-      </c>
-      <c r="Z12" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>D02</v>
+        <v>2026-09-21</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-09-21</v>
+        <v>10:00</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>11:15</v>
       </c>
       <c r="D13" t="str">
-        <v>10:30</v>
+        <v>drive</v>
       </c>
       <c r="E13" t="str">
-        <v>11:00</v>
+        <v>Pickup Sixt → Cassis</v>
       </c>
       <c r="F13" t="str">
-        <v>drive</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Pickup Sixt MRS</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Sixt Marseille Airport</v>
+        <v>Marseille Provence Airport</v>
       </c>
       <c r="I13" t="str">
-        <v>Marseille</v>
+        <v>Cassis</v>
       </c>
       <c r="J13" t="str">
-        <v>MRS rental desk</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Aix-en-Provence</v>
+        <v/>
+      </c>
+      <c r="K13">
+        <v>35</v>
       </c>
       <c r="L13" t="str">
-        <v>SIXT-FR-44102</v>
+        <v>EUR</v>
+      </c>
+      <c r="M13" t="str">
+        <v>planned</v>
       </c>
       <c r="N13" t="str">
-        <v>EUR</v>
+        <v>Airport Sixt; coastal road</v>
       </c>
       <c r="O13" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P13" t="str">
-        <v>Compact auto; full-full</v>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
         <v>rental</v>
       </c>
+      <c r="Q13">
+        <v>43.4393</v>
+      </c>
+      <c r="R13">
+        <v>5.2214</v>
+      </c>
       <c r="S13">
-        <v>43.4393</v>
+        <v>43.2146</v>
       </c>
       <c r="T13">
-        <v>5.2214</v>
-      </c>
-      <c r="U13">
-        <v>43.5263</v>
-      </c>
-      <c r="V13">
-        <v>5.4454</v>
-      </c>
-      <c r="W13" t="str">
-        <v/>
-      </c>
-      <c r="X13" t="str">
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <v/>
-      </c>
-      <c r="Z13" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>5.5387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>H03</v>
+        <v>2026-09-21</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-09-21</v>
+        <v>15:30</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-09-23</v>
+        <v>18:00</v>
       </c>
       <c r="D14" t="str">
-        <v>15:00</v>
+        <v>sight</v>
       </c>
       <c r="E14" t="str">
-        <v>11:00</v>
+        <v>Calanque de Port-Miou</v>
       </c>
       <c r="F14" t="str">
-        <v>hotel</v>
+        <v>Calanque de Port-Miou</v>
       </c>
       <c r="G14" t="str">
-        <v>Hôtel Cézanne</v>
+        <v>Cassis</v>
       </c>
       <c r="H14" t="str">
-        <v>Hôtel Cézanne</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>Aix-en-Provence</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
       <c r="L14" t="str">
-        <v>HCZ-331</v>
-      </c>
-      <c r="M14">
-        <v>320</v>
+        <v>EUR</v>
+      </c>
+      <c r="M14" t="str">
+        <v>planned</v>
       </c>
       <c r="N14" t="str">
-        <v>EUR</v>
+        <v>Easy cliff walk</v>
       </c>
       <c r="O14" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P14" t="str">
-        <v>2 nights Aix base</v>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v>base</v>
-      </c>
-      <c r="S14">
-        <v>43.5263</v>
-      </c>
-      <c r="T14">
-        <v>5.4454</v>
-      </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <v/>
-      </c>
-      <c r="Z14" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>calanques</v>
+      </c>
+      <c r="Q14">
+        <v>43.2089</v>
+      </c>
+      <c r="R14">
+        <v>5.5197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>S04</v>
+        <v>2026-09-21</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-09-21</v>
+        <v>20:00</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D15" t="str">
-        <v>16:30</v>
+        <v>restaurant</v>
       </c>
       <c r="E15" t="str">
-        <v>18:30</v>
+        <v>Seafood Le Grand Large</v>
       </c>
       <c r="F15" t="str">
-        <v>sight</v>
+        <v>Le Grand Large</v>
       </c>
       <c r="G15" t="str">
-        <v>Cours Mirabeau walk</v>
+        <v>Cassis</v>
       </c>
       <c r="H15" t="str">
-        <v>Cours Mirabeau</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>Aix-en-Provence</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
-      <c r="K15" t="str">
-        <v/>
+      <c r="K15">
+        <v>75</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>EUR</v>
+      </c>
+      <c r="M15" t="str">
+        <v>planned</v>
       </c>
       <c r="N15" t="str">
-        <v>EUR</v>
+        <v>Port side</v>
       </c>
       <c r="O15" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P15" t="str">
-        <v>Fountain hop</v>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15">
-        <v>43.5266</v>
-      </c>
-      <c r="T15">
-        <v>5.4474</v>
-      </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
-        <v/>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>seafood</v>
+      </c>
+      <c r="Q15">
+        <v>43.2146</v>
+      </c>
+      <c r="R15">
+        <v>5.5387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>D03</v>
+        <v>2026-09-22</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-22</v>
+        <v>10:00</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>11:00</v>
       </c>
       <c r="D16" t="str">
-        <v>09:00</v>
+        <v>drive</v>
       </c>
       <c r="E16" t="str">
-        <v>10:15</v>
+        <v>Cassis → Aix</v>
       </c>
       <c r="F16" t="str">
-        <v>drive</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>Aix → Pont du Gard</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Cassis</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Aix-en-Provence</v>
       </c>
       <c r="J16" t="str">
-        <v>Aix-en-Provence</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Pont du Gard</v>
+        <v/>
+      </c>
+      <c r="K16">
+        <v>12</v>
       </c>
       <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16">
-        <v>18</v>
+        <v>EUR</v>
+      </c>
+      <c r="M16" t="str">
+        <v>planned</v>
       </c>
       <c r="N16" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O16" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P16" t="str">
-        <v>Toll + parking estimate in cost</v>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="Q16">
+        <v>43.2146</v>
+      </c>
+      <c r="R16">
+        <v>5.5387</v>
       </c>
       <c r="S16">
         <v>43.5263</v>
@@ -1671,120 +1431,81 @@
       <c r="T16">
         <v>5.4454</v>
       </c>
-      <c r="U16">
-        <v>43.9475</v>
-      </c>
-      <c r="V16">
-        <v>4.5356</v>
-      </c>
-      <c r="W16" t="str">
-        <v/>
-      </c>
-      <c r="X16" t="str">
-        <v/>
-      </c>
-      <c r="Y16" t="str">
-        <v/>
-      </c>
-      <c r="Z16" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>S05</v>
+        <v>2026-09-22</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-09-22</v>
+        <v>15:00</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="D17" t="str">
-        <v>10:30</v>
+        <v>sight</v>
       </c>
       <c r="E17" t="str">
-        <v>13:00</v>
+        <v>Cours Mirabeau walk</v>
       </c>
       <c r="F17" t="str">
-        <v>sight</v>
+        <v>Cours Mirabeau</v>
       </c>
       <c r="G17" t="str">
-        <v>Pont du Gard</v>
+        <v>Aix-en-Provence</v>
       </c>
       <c r="H17" t="str">
-        <v>Pont du Gard</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>Vers-Pont-du-Gard</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
       <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17">
-        <v>8</v>
+        <v>EUR</v>
+      </c>
+      <c r="M17" t="str">
+        <v>planned</v>
       </c>
       <c r="N17" t="str">
-        <v>EUR</v>
+        <v>Fountains + plane trees</v>
       </c>
       <c r="O17" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P17" t="str">
-        <v>Bridge + museum</v>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v>unesco</v>
-      </c>
-      <c r="S17">
-        <v>43.9475</v>
-      </c>
-      <c r="T17">
-        <v>4.5356</v>
-      </c>
-      <c r="W17" t="str">
-        <v>Q216753</v>
-      </c>
-      <c r="X17" t="str">
-        <v/>
-      </c>
-      <c r="Y17" t="str">
-        <v/>
-      </c>
-      <c r="Z17" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v/>
+      </c>
+      <c r="Q17">
+        <v>43.5266</v>
+      </c>
+      <c r="R17">
+        <v>5.4474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>D04</v>
+        <v>2026-09-22</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-09-22</v>
+        <v>17:15</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>18:15</v>
       </c>
       <c r="D18" t="str">
-        <v>13:30</v>
+        <v>sight</v>
       </c>
       <c r="E18" t="str">
-        <v>14:15</v>
+        <v>Cathédrale Saint-Sauveur</v>
       </c>
       <c r="F18" t="str">
-        <v>drive</v>
+        <v>Cathédrale Saint-Sauveur</v>
       </c>
       <c r="G18" t="str">
-        <v>Pont du Gard → Avignon</v>
+        <v>Aix-en-Provence</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1793,226 +1514,169 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Pont du Gard</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Avignon</v>
+        <v/>
       </c>
       <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18">
-        <v>12</v>
+        <v>EUR</v>
+      </c>
+      <c r="M18" t="str">
+        <v>planned</v>
       </c>
       <c r="N18" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O18" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
-      <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v/>
-      </c>
-      <c r="S18">
-        <v>43.9475</v>
-      </c>
-      <c r="T18">
-        <v>4.5356</v>
-      </c>
-      <c r="U18">
-        <v>43.9507</v>
-      </c>
-      <c r="V18">
-        <v>4.8075</v>
-      </c>
-      <c r="W18" t="str">
-        <v/>
-      </c>
-      <c r="X18" t="str">
-        <v/>
-      </c>
-      <c r="Y18" t="str">
-        <v/>
-      </c>
-      <c r="Z18" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+      <c r="Q18">
+        <v>43.5315</v>
+      </c>
+      <c r="R18">
+        <v>5.4472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>S06</v>
+        <v>2026-09-22</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-09-22</v>
+        <v>20:00</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D19" t="str">
-        <v>14:30</v>
+        <v>restaurant</v>
       </c>
       <c r="E19" t="str">
-        <v>17:00</v>
+        <v>Dinner Le Passage</v>
       </c>
       <c r="F19" t="str">
-        <v>sight</v>
+        <v>Le Passage</v>
       </c>
       <c r="G19" t="str">
-        <v>Palais des Papes</v>
+        <v>Aix-en-Provence</v>
       </c>
       <c r="H19" t="str">
-        <v>Palais des Papes</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>Avignon</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
-      <c r="K19" t="str">
-        <v/>
+      <c r="K19">
+        <v>60</v>
       </c>
       <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19">
-        <v>14</v>
+        <v>EUR</v>
+      </c>
+      <c r="M19" t="str">
+        <v>planned</v>
       </c>
       <c r="N19" t="str">
-        <v>EUR</v>
+        <v>Courtyard dining</v>
       </c>
       <c r="O19" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v>unesco</v>
-      </c>
-      <c r="S19">
-        <v>43.9507</v>
-      </c>
-      <c r="T19">
-        <v>4.8075</v>
-      </c>
-      <c r="W19" t="str">
-        <v>Q623344</v>
-      </c>
-      <c r="X19" t="str">
-        <v/>
-      </c>
-      <c r="Y19" t="str">
-        <v/>
-      </c>
-      <c r="Z19" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+      <c r="Q19">
+        <v>43.5275</v>
+      </c>
+      <c r="R19">
+        <v>5.4482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>R04</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-09-22</v>
+        <v>09:00</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>10:15</v>
       </c>
       <c r="D20" t="str">
-        <v>20:00</v>
+        <v>drive</v>
       </c>
       <c r="E20" t="str">
-        <v>22:00</v>
+        <v>Aix → Pont du Gard</v>
       </c>
       <c r="F20" t="str">
-        <v>restaurant</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>Dinner Le Passage</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>Le Passage</v>
+        <v>Aix-en-Provence</v>
       </c>
       <c r="I20" t="str">
-        <v>Aix-en-Provence</v>
+        <v>Pont du Gard</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
-      <c r="K20" t="str">
-        <v/>
+      <c r="K20">
+        <v>18</v>
       </c>
       <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20">
-        <v>60</v>
+        <v>EUR</v>
+      </c>
+      <c r="M20" t="str">
+        <v>planned</v>
       </c>
       <c r="N20" t="str">
-        <v>EUR</v>
+        <v>Toll + parking in cost</v>
       </c>
       <c r="O20" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P20" t="str">
-        <v>Back in Aix</v>
-      </c>
-      <c r="Q20" t="str">
-        <v/>
-      </c>
-      <c r="R20" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="Q20">
+        <v>43.5263</v>
+      </c>
+      <c r="R20">
+        <v>5.4454</v>
       </c>
       <c r="S20">
-        <v>43.5275</v>
+        <v>43.9475</v>
       </c>
       <c r="T20">
-        <v>5.4482</v>
-      </c>
-      <c r="W20" t="str">
-        <v/>
-      </c>
-      <c r="X20" t="str">
-        <v/>
-      </c>
-      <c r="Y20" t="str">
-        <v/>
-      </c>
-      <c r="Z20" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>4.5356</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>D05</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-09-23</v>
+        <v>10:30</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>13:00</v>
       </c>
       <c r="D21" t="str">
-        <v>09:30</v>
+        <v>sight</v>
       </c>
       <c r="E21" t="str">
-        <v>10:45</v>
+        <v>Pont du Gard</v>
       </c>
       <c r="F21" t="str">
-        <v>drive</v>
+        <v>Pont du Gard</v>
       </c>
       <c r="G21" t="str">
-        <v>Aix → Arles</v>
+        <v>Vers-Pont-du-Gard</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -2021,226 +1685,172 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Aix-en-Provence</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Arles</v>
+        <v/>
+      </c>
+      <c r="K21">
+        <v>8</v>
       </c>
       <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21">
-        <v>15</v>
+        <v>EUR</v>
+      </c>
+      <c r="M21" t="str">
+        <v>booked</v>
       </c>
       <c r="N21" t="str">
-        <v>EUR</v>
+        <v>Bridge + museum</v>
       </c>
       <c r="O21" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21">
-        <v>43.5263</v>
-      </c>
-      <c r="T21">
-        <v>5.4454</v>
-      </c>
-      <c r="U21">
-        <v>43.6777</v>
-      </c>
-      <c r="V21">
-        <v>4.6309</v>
-      </c>
-      <c r="W21" t="str">
-        <v/>
-      </c>
-      <c r="X21" t="str">
-        <v/>
-      </c>
-      <c r="Y21" t="str">
-        <v/>
-      </c>
-      <c r="Z21" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>unesco</v>
+      </c>
+      <c r="Q21">
+        <v>43.9475</v>
+      </c>
+      <c r="R21">
+        <v>4.5356</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>S07</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-09-23</v>
+        <v>13:30</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>14:15</v>
       </c>
       <c r="D22" t="str">
-        <v>11:00</v>
+        <v>drive</v>
       </c>
       <c r="E22" t="str">
-        <v>13:00</v>
+        <v>Pont du Gard → Avignon</v>
       </c>
       <c r="F22" t="str">
-        <v>sight</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>Arènes d'Arles</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>Arènes d'Arles</v>
+        <v>Pont du Gard</v>
       </c>
       <c r="I22" t="str">
-        <v>Arles</v>
+        <v>Avignon</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
-      <c r="K22" t="str">
-        <v/>
+      <c r="K22">
+        <v>12</v>
       </c>
       <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22">
-        <v>9</v>
+        <v>EUR</v>
+      </c>
+      <c r="M22" t="str">
+        <v>planned</v>
       </c>
       <c r="N22" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O22" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P22" t="str">
-        <v>Roman amphitheatre</v>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v>roman</v>
+        <v/>
+      </c>
+      <c r="Q22">
+        <v>43.9475</v>
+      </c>
+      <c r="R22">
+        <v>4.5356</v>
       </c>
       <c r="S22">
-        <v>43.6777</v>
+        <v>43.9507</v>
       </c>
       <c r="T22">
-        <v>4.6309</v>
-      </c>
-      <c r="W22" t="str">
-        <v>Q636002</v>
-      </c>
-      <c r="X22" t="str">
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <v/>
-      </c>
-      <c r="Z22" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>4.8075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>H04</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-09-23</v>
+        <v>15:30</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-09-25</v>
+        <v>18:00</v>
       </c>
       <c r="D23" t="str">
-        <v>15:00</v>
+        <v>sight</v>
       </c>
       <c r="E23" t="str">
-        <v>10:00</v>
+        <v>Palais des Papes</v>
       </c>
       <c r="F23" t="str">
-        <v>hotel</v>
+        <v>Palais des Papes</v>
       </c>
       <c r="G23" t="str">
-        <v>Maison Volver</v>
+        <v>Avignon</v>
       </c>
       <c r="H23" t="str">
-        <v>Maison Volver</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>Arles</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
-      <c r="K23" t="str">
-        <v/>
+      <c r="K23">
+        <v>14</v>
       </c>
       <c r="L23" t="str">
-        <v>MV-908</v>
-      </c>
-      <c r="M23">
-        <v>260</v>
+        <v>EUR</v>
+      </c>
+      <c r="M23" t="str">
+        <v>planned</v>
       </c>
       <c r="N23" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O23" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P23" t="str">
-        <v>2 nights Arles</v>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v>base</v>
-      </c>
-      <c r="S23">
-        <v>43.6769</v>
-      </c>
-      <c r="T23">
-        <v>4.6276</v>
-      </c>
-      <c r="W23" t="str">
-        <v/>
-      </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <v/>
-      </c>
-      <c r="Z23" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>unesco</v>
+      </c>
+      <c r="Q23">
+        <v>43.9507</v>
+      </c>
+      <c r="R23">
+        <v>4.8075</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>D06</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-09-24</v>
+        <v>20:00</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>22:30</v>
       </c>
       <c r="D24" t="str">
-        <v>09:00</v>
+        <v>restaurant</v>
       </c>
       <c r="E24" t="str">
-        <v>10:00</v>
+        <v>Dinner Christian Etienne</v>
       </c>
       <c r="F24" t="str">
-        <v>drive</v>
+        <v>Christian Etienne</v>
       </c>
       <c r="G24" t="str">
-        <v>Arles → Camargue</v>
+        <v>Avignon</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -2249,152 +1859,116 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Arles</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Parc Ornithologique</v>
+        <v/>
+      </c>
+      <c r="K24">
+        <v>95</v>
       </c>
       <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24">
-        <v>10</v>
+        <v>EUR</v>
+      </c>
+      <c r="M24" t="str">
+        <v>planned</v>
       </c>
       <c r="N24" t="str">
-        <v>EUR</v>
+        <v>Beside the Palais</v>
       </c>
       <c r="O24" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P24" t="str">
-        <v>Flamingo reserve</v>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24">
-        <v>43.6769</v>
-      </c>
-      <c r="T24">
-        <v>4.6276</v>
-      </c>
-      <c r="U24">
-        <v>43.4667</v>
-      </c>
-      <c r="V24">
-        <v>4.4083</v>
-      </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <v/>
-      </c>
-      <c r="Z24" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v/>
+      </c>
+      <c r="Q24">
+        <v>43.9509</v>
+      </c>
+      <c r="R24">
+        <v>4.8069</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>S08</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-09-24</v>
+        <v>09:30</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>10:30</v>
       </c>
       <c r="D25" t="str">
-        <v>10:15</v>
+        <v>drive</v>
       </c>
       <c r="E25" t="str">
-        <v>12:30</v>
+        <v>Avignon → Arles</v>
       </c>
       <c r="F25" t="str">
-        <v>sight</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>Parc Ornithologique</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>Parc Ornithologique du Pont de Gau</v>
+        <v>Avignon</v>
       </c>
       <c r="I25" t="str">
-        <v>Saintes-Maries-de-la-Mer</v>
+        <v>Arles</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
-      <c r="K25" t="str">
-        <v/>
+      <c r="K25">
+        <v>12</v>
       </c>
       <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25">
-        <v>8</v>
+        <v>EUR</v>
+      </c>
+      <c r="M25" t="str">
+        <v>planned</v>
       </c>
       <c r="N25" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O25" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P25" t="str">
         <v/>
       </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v>nature</v>
+      <c r="Q25">
+        <v>43.9495</v>
+      </c>
+      <c r="R25">
+        <v>4.8058</v>
       </c>
       <c r="S25">
-        <v>43.4667</v>
+        <v>43.6777</v>
       </c>
       <c r="T25">
-        <v>4.4083</v>
-      </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <v/>
-      </c>
-      <c r="Z25" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>4.6309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>D07</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-09-24</v>
+        <v>11:00</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>12:30</v>
       </c>
       <c r="D26" t="str">
-        <v>15:00</v>
+        <v>sight</v>
       </c>
       <c r="E26" t="str">
-        <v>16:30</v>
+        <v>Arènes d'Arles</v>
       </c>
       <c r="F26" t="str">
-        <v>drive</v>
+        <v>Arènes d'Arles</v>
       </c>
       <c r="G26" t="str">
-        <v>Camargue → Cassis via coast</v>
+        <v>Arles</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -2403,303 +1977,234 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>Saintes-Maries-de-la-Mer</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Cassis</v>
+        <v/>
+      </c>
+      <c r="K26">
+        <v>9</v>
       </c>
       <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26">
-        <v>25</v>
+        <v>EUR</v>
+      </c>
+      <c r="M26" t="str">
+        <v>planned</v>
       </c>
       <c r="N26" t="str">
-        <v>EUR</v>
+        <v>Roman amphitheatre</v>
       </c>
       <c r="O26" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P26" t="str">
-        <v>Scenic; allow buffer</v>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v>scenic</v>
-      </c>
-      <c r="S26">
-        <v>43.4667</v>
-      </c>
-      <c r="T26">
-        <v>4.4083</v>
-      </c>
-      <c r="U26">
-        <v>43.2146</v>
-      </c>
-      <c r="V26">
-        <v>5.5387</v>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
-      </c>
-      <c r="Z26" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>roman</v>
+      </c>
+      <c r="Q26">
+        <v>43.6777</v>
+      </c>
+      <c r="R26">
+        <v>4.6309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>S09</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-09-24</v>
+        <v>14:00</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>14:45</v>
       </c>
       <c r="D27" t="str">
-        <v>17:00</v>
+        <v>drive</v>
       </c>
       <c r="E27" t="str">
-        <v>19:00</v>
+        <v>Arles → Camargue</v>
       </c>
       <c r="F27" t="str">
-        <v>sight</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>Calanques viewpoint</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>Calanque de Port-Miou</v>
+        <v>Arles</v>
       </c>
       <c r="I27" t="str">
-        <v>Cassis</v>
+        <v>Parc Ornithologique</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
-      <c r="K27" t="str">
-        <v/>
+      <c r="K27">
+        <v>10</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>EUR</v>
+      </c>
+      <c r="M27" t="str">
+        <v>planned</v>
       </c>
       <c r="N27" t="str">
-        <v>EUR</v>
+        <v>Flamingo reserve</v>
       </c>
       <c r="O27" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P27" t="str">
-        <v>Evening light</v>
-      </c>
-      <c r="Q27" t="str">
-        <v/>
-      </c>
-      <c r="R27" t="str">
-        <v>calanques</v>
+        <v/>
+      </c>
+      <c r="Q27">
+        <v>43.6769</v>
+      </c>
+      <c r="R27">
+        <v>4.6276</v>
       </c>
       <c r="S27">
-        <v>43.2089</v>
+        <v>43.4667</v>
       </c>
       <c r="T27">
-        <v>5.5197</v>
-      </c>
-      <c r="W27" t="str">
-        <v/>
-      </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <v/>
-      </c>
-      <c r="Z27" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>4.4083</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>R05</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-09-24</v>
+        <v>15:00</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="D28" t="str">
-        <v>20:00</v>
+        <v>sight</v>
       </c>
       <c r="E28" t="str">
-        <v>22:00</v>
+        <v>Parc Ornithologique</v>
       </c>
       <c r="F28" t="str">
-        <v>restaurant</v>
+        <v>Parc Ornithologique du Pont de Gau</v>
       </c>
       <c r="G28" t="str">
-        <v>Seafood Le Grand Large</v>
+        <v>Saintes-Maries-de-la-Mer</v>
       </c>
       <c r="H28" t="str">
-        <v>Le Grand Large</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>Cassis</v>
+        <v/>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
-      <c r="K28" t="str">
-        <v/>
+      <c r="K28">
+        <v>8</v>
       </c>
       <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28">
-        <v>75</v>
+        <v>EUR</v>
+      </c>
+      <c r="M28" t="str">
+        <v>planned</v>
       </c>
       <c r="N28" t="str">
-        <v>EUR</v>
+        <v/>
       </c>
       <c r="O28" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P28" t="str">
-        <v>Port side</v>
-      </c>
-      <c r="Q28" t="str">
-        <v/>
-      </c>
-      <c r="R28" t="str">
-        <v>seafood</v>
-      </c>
-      <c r="S28">
-        <v>43.2146</v>
-      </c>
-      <c r="T28">
-        <v>5.5387</v>
-      </c>
-      <c r="W28" t="str">
-        <v/>
-      </c>
-      <c r="X28" t="str">
-        <v/>
-      </c>
-      <c r="Y28" t="str">
-        <v/>
-      </c>
-      <c r="Z28" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>nature</v>
+      </c>
+      <c r="Q28">
+        <v>43.4667</v>
+      </c>
+      <c r="R28">
+        <v>4.4083</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>D08</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-09-24</v>
+        <v>17:15</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>18:00</v>
       </c>
       <c r="D29" t="str">
-        <v>22:30</v>
+        <v>drive</v>
       </c>
       <c r="E29" t="str">
-        <v>23:30</v>
+        <v>Camargue → Arles</v>
       </c>
       <c r="F29" t="str">
-        <v>drive</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>Cassis → Arles hotel</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>Parc Ornithologique</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Arles</v>
       </c>
       <c r="J29" t="str">
-        <v>Cassis</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Arles</v>
+        <v/>
+      </c>
+      <c r="K29">
+        <v>8</v>
       </c>
       <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29">
-        <v>20</v>
+        <v>EUR</v>
+      </c>
+      <c r="M29" t="str">
+        <v>planned</v>
       </c>
       <c r="N29" t="str">
-        <v>EUR</v>
+        <v>Back to hotel for dinner</v>
       </c>
       <c r="O29" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P29" t="str">
-        <v>Night return to H04</v>
-      </c>
-      <c r="Q29" t="str">
-        <v/>
-      </c>
-      <c r="R29" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="Q29">
+        <v>43.4667</v>
+      </c>
+      <c r="R29">
+        <v>4.4083</v>
       </c>
       <c r="S29">
-        <v>43.2146</v>
+        <v>43.6769</v>
       </c>
       <c r="T29">
-        <v>5.5387</v>
-      </c>
-      <c r="U29">
-        <v>43.6769</v>
-      </c>
-      <c r="V29">
         <v>4.6276</v>
-      </c>
-      <c r="W29" t="str">
-        <v/>
-      </c>
-      <c r="X29" t="str">
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <v/>
-      </c>
-      <c r="Z29" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>D09</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-09-25</v>
+        <v>20:00</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D30" t="str">
-        <v>10:30</v>
+        <v>restaurant</v>
       </c>
       <c r="E30" t="str">
-        <v>11:45</v>
+        <v>Dinner Le Galoubet</v>
       </c>
       <c r="F30" t="str">
-        <v>drive</v>
+        <v>Le Galoubet</v>
       </c>
       <c r="G30" t="str">
-        <v>Arles → MRS dropoff</v>
+        <v>Arles</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -2708,111 +2213,87 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>Arles</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Marseille Provence Airport</v>
+        <v/>
+      </c>
+      <c r="K30">
+        <v>55</v>
       </c>
       <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30">
-        <v>22</v>
+        <v>EUR</v>
+      </c>
+      <c r="M30" t="str">
+        <v>planned</v>
       </c>
       <c r="N30" t="str">
-        <v>EUR</v>
+        <v>Local Provençal</v>
       </c>
       <c r="O30" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P30" t="str">
-        <v>Fuel before return</v>
-      </c>
-      <c r="Q30" t="str">
-        <v/>
-      </c>
-      <c r="R30" t="str">
-        <v>rental</v>
-      </c>
-      <c r="S30">
-        <v>43.6769</v>
-      </c>
-      <c r="T30">
-        <v>4.6276</v>
-      </c>
-      <c r="U30">
-        <v>43.4393</v>
-      </c>
-      <c r="V30">
-        <v>5.2214</v>
-      </c>
-      <c r="W30" t="str">
-        <v/>
-      </c>
-      <c r="X30" t="str">
-        <v/>
-      </c>
-      <c r="Y30" t="str">
-        <v/>
-      </c>
-      <c r="Z30" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v/>
+      </c>
+      <c r="Q30">
+        <v>43.6772</v>
+      </c>
+      <c r="R30">
+        <v>4.6288</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>F02</v>
+        <v>2026-09-25</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-09-25</v>
+        <v>09:30</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>10:45</v>
       </c>
       <c r="D31" t="str">
-        <v>14:55</v>
+        <v>drive</v>
       </c>
       <c r="E31" t="str">
-        <v>16:35</v>
+        <v>Arles → MRS dropoff</v>
       </c>
       <c r="F31" t="str">
-        <v>flight</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>U2 3825</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>easyJet</v>
+        <v>Arles</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Marseille Provence Airport</v>
       </c>
       <c r="J31" t="str">
-        <v>MRS</v>
-      </c>
-      <c r="K31" t="str">
-        <v>NAP</v>
+        <v/>
+      </c>
+      <c r="K31">
+        <v>22</v>
       </c>
       <c r="L31" t="str">
-        <v>EZY3825-Q1</v>
-      </c>
-      <c r="M31">
-        <v>78</v>
+        <v>EUR</v>
+      </c>
+      <c r="M31" t="str">
+        <v>planned</v>
       </c>
       <c r="N31" t="str">
-        <v>EUR</v>
+        <v>Fuel before return</v>
       </c>
       <c r="O31" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P31" t="str">
-        <v>Cabin bag only</v>
-      </c>
-      <c r="Q31" t="str">
-        <v/>
-      </c>
-      <c r="R31" t="str">
-        <v/>
+        <v>rental</v>
+      </c>
+      <c r="Q31">
+        <v>43.6769</v>
+      </c>
+      <c r="R31">
+        <v>4.6276</v>
       </c>
       <c r="S31">
         <v>43.4393</v>
@@ -2820,387 +2301,701 @@
       <c r="T31">
         <v>5.2214</v>
       </c>
-      <c r="U31">
-        <v>40.884</v>
-      </c>
-      <c r="V31">
-        <v>14.2908</v>
-      </c>
-      <c r="W31" t="str">
-        <v/>
-      </c>
-      <c r="X31" t="str">
-        <v/>
-      </c>
-      <c r="Y31" t="str">
-        <v/>
-      </c>
-      <c r="Z31" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>H05</v>
+        <v>2026-09-25</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-09-25</v>
+        <v>14:55</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-09-26</v>
+        <v>16:35</v>
       </c>
       <c r="D32" t="str">
-        <v>18:00</v>
+        <v>flight</v>
       </c>
       <c r="E32" t="str">
-        <v>11:00</v>
+        <v>U2 3825</v>
       </c>
       <c r="F32" t="str">
-        <v>hotel</v>
+        <v>easyJet</v>
       </c>
       <c r="G32" t="str">
-        <v>Decumano Centro Storico</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>Decumano Centro Storico</v>
+        <v>MRS</v>
       </c>
       <c r="I32" t="str">
-        <v>Naples</v>
+        <v>NAP</v>
       </c>
       <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
+        <v>EZY3825-Q1</v>
+      </c>
+      <c r="K32">
+        <v>78</v>
       </c>
       <c r="L32" t="str">
-        <v>DEC-552</v>
-      </c>
-      <c r="M32">
-        <v>110</v>
+        <v>EUR</v>
+      </c>
+      <c r="M32" t="str">
+        <v>booked</v>
       </c>
       <c r="N32" t="str">
-        <v>EUR</v>
+        <v>Cabin bag only</v>
       </c>
       <c r="O32" t="str">
-        <v>booked</v>
+        <v/>
       </c>
       <c r="P32" t="str">
-        <v>1 night Centro</v>
-      </c>
-      <c r="Q32" t="str">
-        <v/>
-      </c>
-      <c r="R32" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="Q32">
+        <v>43.4393</v>
+      </c>
+      <c r="R32">
+        <v>5.2214</v>
       </c>
       <c r="S32">
-        <v>40.8518</v>
+        <v>40.884</v>
       </c>
       <c r="T32">
-        <v>14.2574</v>
-      </c>
-      <c r="W32" t="str">
-        <v/>
-      </c>
-      <c r="X32" t="str">
-        <v/>
-      </c>
-      <c r="Y32" t="str">
-        <v/>
-      </c>
-      <c r="Z32" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v>14.2908</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>R06</v>
+        <v>2026-09-25</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-09-25</v>
+        <v>20:30</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>22:00</v>
       </c>
       <c r="D33" t="str">
-        <v>20:30</v>
+        <v>restaurant</v>
       </c>
       <c r="E33" t="str">
-        <v>22:00</v>
+        <v>Pizza Sorbillo</v>
       </c>
       <c r="F33" t="str">
-        <v>restaurant</v>
+        <v>Gino Sorbillo</v>
       </c>
       <c r="G33" t="str">
-        <v>Pizza Sorbillo</v>
+        <v>Naples</v>
       </c>
       <c r="H33" t="str">
-        <v>Gino Sorbillo</v>
+        <v/>
       </c>
       <c r="I33" t="str">
-        <v>Naples</v>
+        <v/>
       </c>
       <c r="J33" t="str">
         <v/>
       </c>
-      <c r="K33" t="str">
-        <v/>
+      <c r="K33">
+        <v>25</v>
       </c>
       <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33">
-        <v>25</v>
+        <v>EUR</v>
+      </c>
+      <c r="M33" t="str">
+        <v>planned</v>
       </c>
       <c r="N33" t="str">
-        <v>EUR</v>
+        <v>Via dei Tribunali</v>
       </c>
       <c r="O33" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P33" t="str">
-        <v>Via dei Tribunali</v>
-      </c>
-      <c r="Q33" t="str">
-        <v/>
-      </c>
-      <c r="R33" t="str">
         <v>pizza</v>
       </c>
-      <c r="S33">
+      <c r="Q33">
         <v>40.8506</v>
       </c>
-      <c r="T33">
+      <c r="R33">
         <v>14.2594</v>
-      </c>
-      <c r="W33" t="str">
-        <v/>
-      </c>
-      <c r="X33" t="str">
-        <v/>
-      </c>
-      <c r="Y33" t="str">
-        <v/>
-      </c>
-      <c r="Z33" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>S10</v>
+        <v>2026-09-26</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-09-26</v>
+        <v>09:30</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>12:00</v>
       </c>
       <c r="D34" t="str">
-        <v>09:30</v>
+        <v>sight</v>
       </c>
       <c r="E34" t="str">
-        <v>12:00</v>
+        <v>Spaccanapoli walk</v>
       </c>
       <c r="F34" t="str">
-        <v>sight</v>
+        <v>Spaccanapoli</v>
       </c>
       <c r="G34" t="str">
-        <v>Spaccanapoli walk</v>
+        <v>Naples</v>
       </c>
       <c r="H34" t="str">
-        <v>Spaccanapoli</v>
+        <v/>
       </c>
       <c r="I34" t="str">
-        <v>Naples</v>
+        <v/>
       </c>
       <c r="J34" t="str">
         <v/>
       </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
       <c r="L34" t="str">
-        <v/>
+        <v>EUR</v>
+      </c>
+      <c r="M34" t="str">
+        <v>planned</v>
       </c>
       <c r="N34" t="str">
-        <v>EUR</v>
+        <v>Historic spine of the city</v>
       </c>
       <c r="O34" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P34" t="str">
-        <v>End of sample arc</v>
-      </c>
-      <c r="Q34" t="str">
-        <v/>
-      </c>
-      <c r="R34" t="str">
-        <v/>
-      </c>
-      <c r="S34">
-        <v>40.8496</v>
-      </c>
-      <c r="T34">
-        <v>14.2553</v>
-      </c>
-      <c r="W34" t="str">
-        <v/>
-      </c>
-      <c r="X34" t="str">
-        <v/>
-      </c>
-      <c r="Y34" t="str">
-        <v/>
-      </c>
-      <c r="Z34" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v/>
+      </c>
+      <c r="Q34">
+        <v>40.8495</v>
+      </c>
+      <c r="R34">
+        <v>14.2555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>N01</v>
+        <v>2026-09-26</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-09-26</v>
+        <v>12:30</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>note</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>Trip end — fly home or extend</v>
       </c>
       <c r="F35" t="str">
-        <v>note</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>Trip sample ends</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>Naples</v>
+        <v/>
       </c>
       <c r="J35" t="str">
         <v/>
       </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
       <c r="L35" t="str">
-        <v/>
+        <v>EUR</v>
+      </c>
+      <c r="M35" t="str">
+        <v>planned</v>
       </c>
       <c r="N35" t="str">
-        <v>EUR</v>
+        <v>Duplicate this trip to edit as your own.</v>
       </c>
       <c r="O35" t="str">
-        <v>planned</v>
+        <v/>
       </c>
       <c r="P35" t="str">
-        <v>Fork this example to continue or start blank</v>
-      </c>
-      <c r="Q35" t="str">
-        <v/>
-      </c>
-      <c r="R35" t="str">
-        <v/>
-      </c>
-      <c r="W35" t="str">
-        <v/>
-      </c>
-      <c r="X35" t="str">
-        <v/>
-      </c>
-      <c r="Y35" t="str">
-        <v/>
-      </c>
-      <c r="Z35" t="str">
-        <v>2026-09-10T17:55:43.473Z</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:M9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Column / Value</v>
+        <v>Check-in</v>
       </c>
       <c r="B1" t="str">
-        <v>Meaning</v>
+        <v>Check-out</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Hotel</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Place</v>
+      </c>
+      <c r="E1" t="str">
+        <v>City</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Confirm</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Cost</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Currency</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="K1" t="str">
+        <v>URL</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Lat</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Lon</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Schedule sheet</v>
+        <v>Required · YYYY-MM-DD</v>
       </c>
       <c r="B2" t="str">
-        <v>One row per event in chronological order — the sheet you keep up with</v>
+        <v>Preferred · YYYY-MM-DD (defaults to check-in)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Required · free text</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Optional · booking ref</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Optional · number ≥ 0</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Optional · 3-letter code (EUR)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Optional · planned / booked / done / cancelled</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Optional · https://…</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Optional · decimal degrees</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>type values</v>
+        <v>2026-09-18</v>
       </c>
       <c r="B3" t="str">
-        <v>flight, train, bus, ferry, drive, hotel, sight, restaurant, activity, city, note, other</v>
+        <v>2026-09-20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Hôtel Jeanne d'Arc</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Hôtel Jeanne d'Arc Le Marais</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="F3" t="str">
+        <v>HJD-1942</v>
+      </c>
+      <c r="G3">
+        <v>280</v>
+      </c>
+      <c r="H3" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I3" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2 nights; Marais</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3">
+        <v>48.8555</v>
+      </c>
+      <c r="M3">
+        <v>2.3615</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>status values</v>
+        <v>2026-09-20</v>
       </c>
       <c r="B4" t="str">
-        <v>planned, booked, done, cancelled</v>
+        <v>2026-09-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Hôtel La Résidence du Vieux-Port</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Hôtel La Résidence du Vieux-Port</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Marseille</v>
+      </c>
+      <c r="F4" t="str">
+        <v>RVP-441</v>
+      </c>
+      <c r="G4">
+        <v>160</v>
+      </c>
+      <c r="H4" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I4" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J4" t="str">
+        <v>1 night harbour view</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4">
+        <v>43.2951</v>
+      </c>
+      <c r="M4">
+        <v>5.3738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>from / to</v>
+        <v>2026-09-21</v>
       </c>
       <c r="B5" t="str">
-        <v>For flights use IATA (TLV, CDG). For drives use place names</v>
+        <v>2026-09-22</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Les Roches Blanches</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Hôtel Les Roches Blanches</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Cassis</v>
+      </c>
+      <c r="F5" t="str">
+        <v>LRB-221</v>
+      </c>
+      <c r="G5">
+        <v>220</v>
+      </c>
+      <c r="H5" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I5" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1 night above the calanques</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5">
+        <v>43.2085</v>
+      </c>
+      <c r="M5">
+        <v>5.529</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>end_date</v>
+        <v>2026-09-22</v>
       </c>
       <c r="B6" t="str">
-        <v>Hotel checkout or overnight flight/train arrival date</v>
+        <v>2026-09-23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Hôtel Cézanne</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Hôtel Cézanne</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Aix-en-Provence</v>
+      </c>
+      <c r="F6" t="str">
+        <v>CEZ-77</v>
+      </c>
+      <c r="G6">
+        <v>190</v>
+      </c>
+      <c r="H6" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I6" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1 night centre</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>43.5263</v>
+      </c>
+      <c r="M6">
+        <v>5.4454</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>lat / lon</v>
+        <v>2026-09-23</v>
       </c>
       <c r="B7" t="str">
-        <v>Optional; app fills on enrich/export</v>
+        <v>2026-09-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Hôtel de l’Horloge</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Hôtel de l'Horloge</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Avignon</v>
+      </c>
+      <c r="F7" t="str">
+        <v>HOR-309</v>
+      </c>
+      <c r="G7">
+        <v>175</v>
+      </c>
+      <c r="H7" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I7" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J7" t="str">
+        <v>1 night near Palais</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7">
+        <v>43.9495</v>
+      </c>
+      <c r="M7">
+        <v>4.8058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>All times</v>
+        <v>2026-09-24</v>
       </c>
       <c r="B8" t="str">
-        <v>Local wall clock — never UTC in this workbook</v>
+        <v>2026-09-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Maison Volver</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Maison Volver</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Arles</v>
+      </c>
+      <c r="F8" t="str">
+        <v>MV-908</v>
+      </c>
+      <c r="G8">
+        <v>160</v>
+      </c>
+      <c r="H8" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I8" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1 night old town</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>43.6769</v>
+      </c>
+      <c r="M8">
+        <v>4.6276</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Decumano Centro Storico</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Decumano Centro Storico</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Naples</v>
+      </c>
+      <c r="F9" t="str">
+        <v>DEC-552</v>
+      </c>
+      <c r="G9">
+        <v>110</v>
+      </c>
+      <c r="H9" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I9" t="str">
+        <v>booked</v>
+      </c>
+      <c r="J9" t="str">
+        <v>1 night Centro</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9">
+        <v>40.8518</v>
+      </c>
+      <c r="M9">
+        <v>14.2574</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Cash snapshot (export only — ignored when importing)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Amounts as entered (no FX conversion)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>By type</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Total</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="B5">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="B6">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>flight</v>
+      </c>
+      <c r="B7">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>drive</v>
+      </c>
+      <c r="B8">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>train</v>
+      </c>
+      <c r="B9">
+        <v>100.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>sight</v>
+      </c>
+      <c r="B10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>By currency</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Total</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="B13">
+        <v>2642.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>